--- a/templates/nre_template.xlsx
+++ b/templates/nre_template.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -440,6 +440,8 @@
     <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,40 +462,50 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Duration_for_NRE</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Lab_Rate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Lab_Fee</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Total_Fee</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Phase</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Functionality</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gold_Rail_Selection</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Ufit_for_SoR</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Final_Fee</t>
         </is>

--- a/templates/nre_template.xlsx
+++ b/templates/nre_template.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M1"/>
+  <dimension ref="A1:T5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -502,7 +502,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Ufit_for_SoR</t>
+          <t>Only_ORv3_MGX_Mini_Rack_wo_L11_Rack</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
@@ -511,6 +511,10 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -522,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,7 +535,6 @@
           <t>Account</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,7 +542,6 @@
           <t>System_Weight_kg</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -547,7 +549,6 @@
           <t>Selected_Phases</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -555,15 +556,13 @@
           <t>Gold_Rail_Selection</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ufit_for_SoR</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
+          <t>Only_ORv3_MGX_Mini_Rack_wo_L11_Rack</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -571,7 +570,6 @@
           <t>Grand_Total_Fee</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
